--- a/gut/data/gut_cases.xlsx
+++ b/gut/data/gut_cases.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The one file where everything points the same way. Easy for the gut, easy for the rule. Cases like this teach the gut false confidence.</t>
+          <t>The one file where everything points the same way. Easy for the gut, easy for the rule, and cases like this are where false confidence comes from.</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Even crude models with unit weights tend to outperform the experts who built them, because they never get tired, bored, or charmed.</t>
+          <t>Even crude models with unit weights tend to outperform the experts who built them.</t>
         </is>
       </c>
     </row>
